--- a/DealerOS_畫面總表_Stitch_Mapping.xlsx
+++ b/DealerOS_畫面總表_Stitch_Mapping.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ming/Documents/claude/Russell_Car_CRM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ming/Documents/claude/cicd_pipeline_poc/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{770E241E-EB69-4446-9BDD-5748E2FD934F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="畫面總表" sheetId="1" r:id="rId1"/>
@@ -2250,7 +2250,7 @@
     <col min="11" max="11" width="64.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="36">
+    <row r="1" spans="1:11" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="34">
+    <row r="9" spans="1:11" ht="17">
       <c r="A9" s="12" t="s">
         <v>53</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="34">
+    <row r="10" spans="1:11" ht="17">
       <c r="A10" s="14" t="s">
         <v>56</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="34">
+    <row r="11" spans="1:11" ht="17">
       <c r="A11" s="14" t="s">
         <v>64</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="51">
+    <row r="17" spans="1:11" ht="17">
       <c r="A17" s="16" t="s">
         <v>94</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="34">
+    <row r="20" spans="1:11" ht="17">
       <c r="A20" s="16" t="s">
         <v>113</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="34">
+    <row r="22" spans="1:11" ht="17">
       <c r="A22" s="16" t="s">
         <v>126</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="34">
+    <row r="34" spans="1:11" ht="17">
       <c r="A34" s="23" t="s">
         <v>189</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="34">
+    <row r="40" spans="1:11" ht="17">
       <c r="A40" s="29" t="s">
         <v>224</v>
       </c>
